--- a/Trắc nghiệm ôn luyện/BA Technical/multiple_choice_sample_template_PROCESS_MODELING.xlsx
+++ b/Trắc nghiệm ôn luyện/BA Technical/multiple_choice_sample_template_PROCESS_MODELING.xlsx
@@ -447,7 +447,7 @@
         <v>Tài liệu SRS (Software Requirement Specification) trong dự án phần mềm phục vụ mục đích chính là gì?</v>
       </c>
       <c r="C2" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D2" t="str">
         <v>SRS là tài liệu đặc tả yêu cầu phần mềm, làm hợp đồng kỹ thuật chi tiết giữa đội phát triển (dev, test) và khách hàng.</v>
@@ -476,7 +476,7 @@
         <v>Trong sơ đồ Use Case của UML, ký hiệu nào được dùng để biểu diễn tác nhân (Actor) bên ngoài tương tác với hệ thống?</v>
       </c>
       <c r="C3" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D3" t="str">
         <v>Trong sơ đồ Use Case, Actor được biểu diễn bằng hình người que đại diện cho vai trò tương tác với hệ thống.</v>
@@ -505,7 +505,7 @@
         <v>Tài liệu BRD (Business Requirement Document) khác tài liệu SRS ở điểm cốt lõi nào?</v>
       </c>
       <c r="C4" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D4" t="str">
         <v>BRD mô tả bài toán kinh doanh và mục tiêu chiến lược (cấp cao, phi kỹ thuật). SRS chuyển hóa BRD thành các yêu cầu phần mềm chi tiết cho đội dev/test.</v>
@@ -534,7 +534,7 @@
         <v>Trong sơ đồ Use Case, mối quan hệ `&lt;&lt;include&gt;&gt;` giữa hai Use Case A và B có ý nghĩa gì?</v>
       </c>
       <c r="C5" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D5" t="str">
         <v>Mối quan hệ `&lt;&lt;include&gt;&gt;` biểu diễn hành vi bắt buộc. Khi Use Case A chạy, nó bắt buộc phải gọi Use Case B như một phần trong luồng xử lý của mình.</v>
@@ -563,7 +563,7 @@
         <v>Trong sơ đồ Use Case, mối quan hệ `&lt;&lt;extend&gt;&gt;` giữa hai Use Case B và A (B extend A) có ý nghĩa gì?</v>
       </c>
       <c r="C6" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D6" t="str">
         <v>Mối quan hệ `&lt;&lt;extend&gt;&gt;` mô tả hành vi tùy chọn, bổ sung vào Use Case gốc tại các điểm mở rộng khi điều kiện cụ thể được đáp ứng.</v>
@@ -592,7 +592,7 @@
         <v>Khi vẽ sơ đồ Use Case, "System Boundary" (Biên hệ thống) được biểu diễn bằng hình gì và có vai trò gì?</v>
       </c>
       <c r="C7" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D7" t="str">
         <v>System Boundary (đường biên hệ thống) được vẽ bằng hình chữ nhật để phân định rõ ràng những gì thuộc về hệ thống bên trong và những gì nằm ngoài hệ thống.</v>
@@ -621,7 +621,7 @@
         <v>Hoạt động "UAT" (User Acceptance Testing) trong quy trình bàn giao phần mềm là gì?</v>
       </c>
       <c r="C8" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D8" t="str">
         <v>UAT là giai đoạn kiểm thử cuối cùng trước khi go-live, nơi người dùng cuối hoặc khách hàng chạy thử để xác nhận phần mềm đáp ứng đúng yêu cầu của họ.</v>
@@ -650,7 +650,7 @@
         <v>Tài liệu "UAT Test Cases" (hoặc UAT Scenarios) do BA soạn thảo thường dựa trên căn cứ trực tiếp nào?</v>
       </c>
       <c r="C9" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D9" t="str">
         <v>UAT Scenarios phải dựa trên tài liệu đặc tả yêu cầu nghiệp vụ (SRS/User Stories/AC) để xác thực xem hệ thống có chạy đúng nghiệp vụ đã chốt hay không.</v>
@@ -679,7 +679,7 @@
         <v>Trong sơ đồ Use Case, một Actor có thể kế thừa (Generalization) từ một Actor khác không và ý nghĩa là gì?</v>
       </c>
       <c r="C10" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D10" t="str">
         <v>Actor Generalization cho phép thiết lập phân quyền. Ví dụ: Admin kế thừa từ User, nghĩa là Admin tự động có quyền thực hiện tất cả Use Case mà User được phép làm.</v>
@@ -708,7 +708,7 @@
         <v>Khi viết tài liệu mô tả chi tiết Use Case (Use Case Specification), phần "Pre-conditions" và "Post-conditions" định nghĩa điều gì?</v>
       </c>
       <c r="C11" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D11" t="str">
         <v>Pre-condition thiết lập bối cảnh cần thiết (ví dụ: Người dùng đã đăng nhập). Post-condition đảm bảo dữ liệu/hệ thống đạt trạng thái mong muốn sau khi Use Case chạy xong (ví dụ: Đơn hàng được tạo và lưu vào DB).</v>
@@ -737,7 +737,7 @@
         <v>Sự khác biệt giữa Luồng cơ bản (Basic Flow), Luồng thay thế (Alternative Flow) và Luồng lỗi (Exception Flow) trong tài liệu đặc tả Use Case là gì?</v>
       </c>
       <c r="C12" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D12" t="str">
         <v>Basic Flow đi thẳng đến mục tiêu thành công. Alternative Flow cũng dẫn đến thành công nhưng qua các bước khác. Exception Flow xử lý các lỗi phát sinh ngăn cản đạt mục tiêu Use Case.</v>
@@ -766,7 +766,7 @@
         <v>Trong sơ đồ Use Case, nếu một Actor kết nối với một Use Case nằm ngoài phạm vi System Boundary thì lỗi thiết kế nào đang xảy ra?</v>
       </c>
       <c r="C13" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D13" t="str">
         <v>System Boundary bao quanh các tính năng hệ thống xây dựng. Use Case nằm ngoài đường biên không thuộc phạm vi dự án, do đó vẽ kết nối ra ngoài là sai thiết kế.</v>
@@ -795,7 +795,7 @@
         <v>Để viết một tài liệu SRS đạt chuẩn chất lượng theo chuẩn IEEE 830, cấu trúc tài liệu bắt buộc phải bao gồm những phần chính nào sau đây?</v>
       </c>
       <c r="C14" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D14" t="str">
         <v>Chuẩn IEEE 830 quy định cấu trúc SRS chuẩn gồm 3 phần chính: Giới thiệu dự án, Mô tả tổng quan kiến trúc và đặc tả chi tiết các yêu cầu kỹ thuật.</v>
@@ -824,7 +824,7 @@
         <v>Trong giai đoạn chuẩn bị cho UAT, nếu khách hàng yêu cầu kiểm thử các kịch bản không hề có trong tài liệu SRS đã thống nhất từ trước, BA nên ứng phó ra sao?</v>
       </c>
       <c r="C15" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D15" t="str">
         <v>UAT nghiệm thu dựa trên scope đã thống nhất. Các yêu cầu mới phát sinh ngoài SRS phải đi qua quy trình Change Request để tránh phình to phạm vi dự án một cách mất kiểm soát.</v>
@@ -853,7 +853,7 @@
         <v>Khi viết tài liệu đặc tả API nghiệp vụ cho đội ngũ phát triển Frontend và Backend, thông tin nào sau đây là quan trọng nhất BA cần cung cấp?</v>
       </c>
       <c r="C16" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D16" t="str">
         <v>Đặc tả API của BA đóng vai trò là giao kèo tích hợp (Contract) giữa FE và BE. Cần chỉ rõ URL, method, cấu trúc JSON đầu vào và đầu ra để hai bên phát triển song song.</v>
@@ -882,7 +882,7 @@
         <v>Trong sơ đồ Use Case, sự khác biệt giữa quan hệ "Association" và quan hệ "Dependency" (`&lt;&lt;include&gt;&gt;`/`&lt;&lt;extend&gt;&gt;`) là gì?</v>
       </c>
       <c r="C17" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D17" t="str">
         <v>Đường Association (nét liền không mũi tên) kết nối Actor với Use Case để chỉ ra sự tương tác. Đường nét đứt có mũi tên (`&lt;&lt;include&gt;&gt;`/`&lt;&lt;extend&gt;&gt;`) chỉ sự phụ thuộc logic giữa các Use Case.</v>
@@ -911,7 +911,7 @@
         <v>Khi tổ chức buổi họp nghiệm thu UAT, vai trò chủ chốt của BA trong buổi họp này là gì?</v>
       </c>
       <c r="C18" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D18" t="str">
         <v>BA hỗ trợ điều phối UAT, giải thích nghiệp vụ, xác định xem lỗi phát sinh là Bug (sai SRS) hay CR (yêu cầu mới ngoài SRS) và lập biên bản nghiệm thu.</v>
@@ -940,7 +940,7 @@
         <v>Một hệ thống ngân hàng có Use Case "Rút tiền". Use Case này có quan hệ `&lt;&lt;include&gt;&gt;` với "Xác thực mã PIN" và `&lt;&lt;extend&gt;&gt;` với "In biên lai". Hãy chỉ ra hành vi của hệ thống khi ATM bị hết giấy in biên lai.</v>
       </c>
       <c r="C19" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D19" t="str">
         <v>Vì "In biên lai" là quan hệ `&lt;&lt;extend&gt;&gt;` (tùy chọn), lỗi không in được biên lai không ảnh hưởng đến việc hoàn thành Use Case chính "Rút tiền". Ngược lại, nếu lỗi ở Use Case include "Xác thực mã PIN", giao dịch sẽ thất bại ngay lập tức.</v>
@@ -969,7 +969,7 @@
         <v>Phân tích sơ đồ Use Case sau: Use Case "Đăng nhập" có quan hệ `&lt;&lt;extend&gt;&gt;` đến Use Case "Đăng nhập sai 3 lần" (với điều kiện mở rộng là số lần sai &gt;= 3). Làm thế nào để đặc tả luồng này trong tài liệu Use Case Specification?</v>
       </c>
       <c r="C20" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D20" t="str">
         <v>Khi đặc tả quan hệ `&lt;&lt;extend&gt;&gt;`, tài liệu Use Case Specification của Use Case gốc cần chỉ rõ Extension Point (Vị trí mở rộng trong luồng) và điều kiện cụ thể để kích hoạt Use Case mở rộng.</v>
@@ -998,7 +998,7 @@
         <v>Khi bàn giao hệ thống ERP cho khách hàng chạy UAT, khách hàng phản ánh rằng phần mềm chạy đúng theo tài liệu SRS nhưng họ không thể sử dụng được vì quy trình thực tế đã thay đổi. Lỗi này thuộc về giai đoạn nào và BA xử lý thế nào?</v>
       </c>
       <c r="C21" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D21" t="str">
         <v>Nếu phần mềm đúng SRS nhưng sai thực tế, tức là SRS đã bị lỗi thời hoặc BA khơi gợi yêu cầu sai (thiếu Validation động). BA cần xử lý theo quy trình quản lý thay đổi (CR) để cập nhật hệ thống.</v>
@@ -1027,7 +1027,7 @@
         <v>Tại sao việc lạm dụng quá nhiều quan hệ `&lt;&lt;extend&gt;&gt;` và `&lt;&lt;include&gt;&gt;` trong sơ đồ Use Case được coi là một phản mẫu (Anti-pattern) trong phân tích thiết kế?</v>
       </c>
       <c r="C22" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D22" t="str">
         <v>Sơ đồ Use Case sinh ra để khách hàng hiểu được hệ thống làm gì. Việc lạm dụng chi tiết hóa include/extend biến nó thành sơ đồ thiết kế thuật toán kỹ thuật, mất đi tính giao tiếp nghiệp vụ.</v>
@@ -1056,7 +1056,7 @@
         <v>Trong tài liệu SRS, yêu cầu phi chức năng về tính khả dụng (Usability) thường được lượng hóa thông qua tiêu chí cụ thể nào dưới đây để đảm bảo tính kiểm thử được?</v>
       </c>
       <c r="C23" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D23" t="str">
         <v>Usability đo lường tính dễ dùng. Để test được, nó phải được lượng hóa thông qua thời gian hoàn thành tác vụ (Task completion time), tỷ lệ lỗi của người dùng (Error rate) và thời gian học sử dụng (Learning curve).</v>
@@ -1085,7 +1085,7 @@
         <v>Khi viết tài liệu đặc tả Data Mapping giữa hệ thống thương mại điện tử mới và hệ thống thanh toán của bên thứ ba, BA cần chỉ rõ thông tin nào để đảm bảo tính toàn vẹn dữ liệu?</v>
       </c>
       <c r="C24" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D24" t="str">
         <v>Data Mapping chi tiết (Source Field, Target Field, Type, Rules, Nullability) là bắt buộc để lập trình viên viết code chuyển đổi dữ liệu chính xác, tránh mất mát thông tin hoặc lỗi kiểu dữ liệu ở runtime.</v>
@@ -1114,7 +1114,7 @@
         <v>Trong tài liệu mô tả Use Case, luồng phụ "Sub-flow" khác với luồng thay thế "Alternative Flow" ở điểm cốt lõi nào?</v>
       </c>
       <c r="C25" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D25" t="str">
         <v>Sub-flow giúp chia nhỏ luồng cơ bản dài thành các khối logic tuần tự dễ quản lý. Alternative Flow là nhánh rẽ nghiệp vụ tùy chọn dựa trên quyết định/điều kiện cụ thể.</v>
@@ -1143,7 +1143,7 @@
         <v>Khi viết tài liệu SRS cho hệ thống Microservices, BA xử lý phần đặc tả giao tiếp giữa các dịch vụ (Inter-service communication) như thế nào?</v>
       </c>
       <c r="C26" t="str">
-        <v>BA Documentation</v>
+        <v>BA Process Modeling</v>
       </c>
       <c r="D26" t="str">
         <v>Mặc dù là hệ thống kỹ thuật, luồng đi của nghiệp vụ qua các service và dữ liệu trao đổi (Payload) quyết định tính đúng đắn của tính năng. BA cần đặc tả rõ ràng luồng tích hợp này.</v>

--- a/Trắc nghiệm ôn luyện/BA Technical/multiple_choice_sample_template_PROCESS_MODELING.xlsx
+++ b/Trắc nghiệm ôn luyện/BA Technical/multiple_choice_sample_template_PROCESS_MODELING.xlsx
@@ -511,7 +511,7 @@
         <v>BRD mô tả bài toán kinh doanh và mục tiêu chiến lược (cấp cao, phi kỹ thuật). SRS chuyển hóa BRD thành các yêu cầu phần mềm chi tiết cho đội dev/test.</v>
       </c>
       <c r="E4" t="str">
-        <v>BRD tập trung vào nhu cầu và mục tiêu kinh doanh cấp cao của tổ chức; SRS tập trung vào đặc tả kỹ thuật và hành vi chi tiết của phần mềm</v>
+        <v>BRD dùng cho giai đoạn kết thúc dự án; SRS dùng cho giai đoạn bắt đầu dự án</v>
       </c>
       <c r="F4" t="str">
         <v>BRD do lập trình viên viết để hướng dẫn code; SRS do khách hàng viết để đặt hàng phần mềm</v>
@@ -520,10 +520,10 @@
         <v>BRD chỉ chứa các bản vẽ thiết kế giao diện; SRS chỉ chứa mã nguồn phần mềm</v>
       </c>
       <c r="H4" t="str">
-        <v>BRD dùng cho giai đoạn kết thúc dự án; SRS dùng cho giai đoạn bắt đầu dự án</v>
+        <v>BRD tập trung vào nhu cầu và mục tiêu kinh doanh cấp cao của tổ chức; SRS tập trung vào đặc tả kỹ thuật và hành vi chi tiết của phần mềm</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>Mối quan hệ `&lt;&lt;include&gt;&gt;` biểu diễn hành vi bắt buộc. Khi Use Case A chạy, nó bắt buộc phải gọi Use Case B như một phần trong luồng xử lý của mình.</v>
       </c>
       <c r="E5" t="str">
+        <v>Use Case B là chức năng tùy chọn, chỉ chạy trong một số điều kiện nhất định của Use Case A</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Use Case B kế thừa toàn bộ hành vi và cấu trúc dữ liệu từ Use Case A</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Use Case B được thực hiện hoàn toàn song song và độc lập không liên quan đến Use Case A</v>
+      </c>
+      <c r="H5" t="str">
         <v>Use Case B là chức năng bắt buộc phải thực hiện trong luồng chạy của Use Case A — không thể hoàn thành A nếu thiếu B</v>
       </c>
-      <c r="F5" t="str">
-        <v>Use Case B là chức năng tùy chọn, chỉ chạy trong một số điều kiện nhất định của Use Case A</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Use Case B kế thừa toàn bộ hành vi và cấu trúc dữ liệu từ Use Case A</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Use Case B được thực hiện hoàn toàn song song và độc lập không liên quan đến Use Case A</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>Mối quan hệ `&lt;&lt;extend&gt;&gt;` mô tả hành vi tùy chọn, bổ sung vào Use Case gốc tại các điểm mở rộng khi điều kiện cụ thể được đáp ứng.</v>
       </c>
       <c r="E6" t="str">
-        <v>Use Case B là hành vi mở rộng tùy chọn của Use Case A, chỉ được gọi khi thỏa mãn điều kiện nhất định (Extension Point)</v>
+        <v>Use Case B là một dạng thiết kế giao diện người dùng thay thế cho Use Case A</v>
       </c>
       <c r="F6" t="str">
         <v>Use Case B là bước bắt buộc phải chạy trước khi Use Case A được phép kích hoạt</v>
       </c>
       <c r="G6" t="str">
-        <v>Use Case B là một dạng thiết kế giao diện người dùng thay thế cho Use Case A</v>
+        <v>Use Case B là hành vi mở rộng tùy chọn của Use Case A, chỉ được gọi khi thỏa mãn điều kiện nhất định (Extension Point)</v>
       </c>
       <c r="H6" t="str">
         <v>Use Case B đại diện cho một tác nhân phần cứng bên ngoài hệ thống</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>System Boundary (đường biên hệ thống) được vẽ bằng hình chữ nhật để phân định rõ ràng những gì thuộc về hệ thống bên trong và những gì nằm ngoài hệ thống.</v>
       </c>
       <c r="E7" t="str">
+        <v>Đường mũi tên nét đứt — dùng để kết nối Actor với Use Case</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Hình thoi màu đen — biểu thị mối quan hệ composite trong hệ thống database</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Hình elip bao quanh các Actor — dùng để phân nhóm người dùng theo phòng ban</v>
+      </c>
+      <c r="H7" t="str">
         <v>Hình chữ nhật bao quanh các Use Case — dùng để xác định phạm vi của hệ thống đang phát triển, phân tách với các Actor bên ngoài</v>
       </c>
-      <c r="F7" t="str">
-        <v>Hình elip bao quanh các Actor — dùng để phân nhóm người dùng theo phòng ban</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Đường mũi tên nét đứt — dùng để kết nối Actor với Use Case</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Hình thoi màu đen — biểu thị mối quan hệ composite trong hệ thống database</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>UAT là giai đoạn kiểm thử cuối cùng trước khi go-live, nơi người dùng cuối hoặc khách hàng chạy thử để xác nhận phần mềm đáp ứng đúng yêu cầu của họ.</v>
       </c>
       <c r="E8" t="str">
+        <v>Kiểm thử hiệu năng — đo lường giới hạn chịu tải tối đa của máy chủ vật lý</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Quá trình cài đặt mã nguồn lên môi trường Production của doanh nghiệp</v>
+      </c>
+      <c r="G8" t="str">
         <v>Kiểm thử chấp nhận người dùng — khách hàng trực tiếp chạy thử phần mềm dựa trên kịch bản nghiệp vụ để xác nhận nghiệm thu</v>
       </c>
-      <c r="F8" t="str">
+      <c r="H8" t="str">
         <v>Kiểm thử tích hợp hệ thống — dev kiểm tra các API kết nối giữa các module</v>
       </c>
-      <c r="G8" t="str">
-        <v>Kiểm thử hiệu năng — đo lường giới hạn chịu tải tối đa của máy chủ vật lý</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Quá trình cài đặt mã nguồn lên môi trường Production của doanh nghiệp</v>
-      </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -656,19 +656,19 @@
         <v>UAT Scenarios phải dựa trên tài liệu đặc tả yêu cầu nghiệp vụ (SRS/User Stories/AC) để xác thực xem hệ thống có chạy đúng nghiệp vụ đã chốt hay không.</v>
       </c>
       <c r="E9" t="str">
+        <v>Mã nguồn lập trình thực tế của lập trình viên — đảm bảo kiểm thử hết các hàm logic</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Sơ đồ tổ chức nhân sự của khách hàng — đảm bảo phân quyền người dùng</v>
+      </c>
+      <c r="G9" t="str">
         <v>Tài liệu SRS và các tiêu chí nghiệm thu (Acceptance Criteria) của User Story — đảm bảo kiểm tra đúng cam kết nghiệp vụ</v>
       </c>
-      <c r="F9" t="str">
+      <c r="H9" t="str">
         <v>Cấu trúc bảng cơ sở dữ liệu chi tiết của hệ thống cũ — đảm bảo đồng bộ trường dữ liệu</v>
       </c>
-      <c r="G9" t="str">
-        <v>Sơ đồ tổ chức nhân sự của khách hàng — đảm bảo phân quyền người dùng</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Mã nguồn lập trình thực tế của lập trình viên — đảm bảo kiểm thử hết các hàm logic</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -685,7 +685,7 @@
         <v>Actor Generalization cho phép thiết lập phân quyền. Ví dụ: Admin kế thừa từ User, nghĩa là Admin tự động có quyền thực hiện tất cả Use Case mà User được phép làm.</v>
       </c>
       <c r="E10" t="str">
-        <v>Có — Actor con sẽ thừa hưởng toàn bộ quyền tương tác với các Use Case của Actor cha</v>
+        <v>Có — nhưng Actor con bắt buộc phải ghi đè (override) tất cả Use Case của Actor cha</v>
       </c>
       <c r="F10" t="str">
         <v>Không — Actor chỉ là người dùng bên ngoài nên không có quan hệ kế thừa</v>
@@ -694,10 +694,10 @@
         <v>Có — nhưng chỉ áp dụng nếu Actor cha là một hệ thống phần cứng khác</v>
       </c>
       <c r="H10" t="str">
-        <v>Có — nhưng Actor con bắt buộc phải ghi đè (override) tất cả Use Case của Actor cha</v>
+        <v>Có — Actor con sẽ thừa hưởng toàn bộ quyền tương tác với các Use Case của Actor cha</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Pre-condition thiết lập bối cảnh cần thiết (ví dụ: Người dùng đã đăng nhập). Post-condition đảm bảo dữ liệu/hệ thống đạt trạng thái mong muốn sau khi Use Case chạy xong (ví dụ: Đơn hàng được tạo và lưu vào DB).</v>
       </c>
       <c r="E11" t="str">
+        <v>Pre-conditions: Cuộc họp chuẩn bị yêu cầu; Post-conditions: Cuộc họp nghiệm thu bàn giao tính năng</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Pre-conditions: Cấu hình phần cứng tối thiểu; Post-conditions: Cấu hình phần mềm khuyên dùng</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Pre-conditions: Các bước nhập dữ liệu của người dùng; Post-conditions: Các thông báo lỗi hiển thị trên màn hình</v>
+      </c>
+      <c r="H11" t="str">
         <v>Pre-conditions: Điều kiện hệ thống bắt buộc phải thỏa mãn TRƯỚC KHI Use Case được kích hoạt; Post-conditions: Trạng thái hệ thống đạt được SAU KHI Use Case hoàn thành thành công</v>
       </c>
-      <c r="F11" t="str">
-        <v>Pre-conditions: Các bước nhập dữ liệu của người dùng; Post-conditions: Các thông báo lỗi hiển thị trên màn hình</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Pre-conditions: Cấu hình phần cứng tối thiểu; Post-conditions: Cấu hình phần mềm khuyên dùng</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Pre-conditions: Cuộc họp chuẩn bị yêu cầu; Post-conditions: Cuộc họp nghiệm thu bàn giao tính năng</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>Basic Flow đi thẳng đến mục tiêu thành công. Alternative Flow cũng dẫn đến thành công nhưng qua các bước khác. Exception Flow xử lý các lỗi phát sinh ngăn cản đạt mục tiêu Use Case.</v>
       </c>
       <c r="E12" t="str">
+        <v>Basic: Luồng dành cho User; Alternative: Luồng dành cho Admin; Exception: Luồng dành cho Developer</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Basic: Thiết kế giao diện; Alternative: Cấu trúc cơ sở dữ liệu; Exception: Kịch bản kiểm thử</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Basic: Lập trình Frontend; Alternative: Lập trình Backend; Exception: Cấu hình Deploy server</v>
+      </c>
+      <c r="H12" t="str">
         <v>Basic: Luồng thành công chính (Happy Path); Alternative: Các luồng thành công khác; Exception: Luồng xử lý lỗi/ngoại lệ dừng hệ thống</v>
       </c>
-      <c r="F12" t="str">
-        <v>Basic: Luồng dành cho User; Alternative: Luồng dành cho Admin; Exception: Luồng dành cho Developer</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Basic: Thiết kế giao diện; Alternative: Cấu trúc cơ sở dữ liệu; Exception: Kịch bản kiểm thử</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Basic: Lập trình Frontend; Alternative: Lập trình Backend; Exception: Cấu hình Deploy server</v>
-      </c>
       <c r="I12">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -772,19 +772,19 @@
         <v>System Boundary bao quanh các tính năng hệ thống xây dựng. Use Case nằm ngoài đường biên không thuộc phạm vi dự án, do đó vẽ kết nối ra ngoài là sai thiết kế.</v>
       </c>
       <c r="E13" t="str">
+        <v>Lỗi thiếu quan hệ kế thừa giữa các Use Case tương ứng</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Lỗi sử dụng sai ký hiệu Actor (người que) thay cho ký hiệu hệ thống</v>
+      </c>
+      <c r="G13" t="str">
         <v>Không có lỗi vì Actor có thể tương tác với bất kỳ đối tượng nào</v>
       </c>
-      <c r="F13" t="str">
+      <c r="H13" t="str">
         <v>Lỗi vi phạm ranh giới hệ thống — mọi Use Case của hệ thống phát triển bắt buộc phải nằm TRONG System Boundary; Actor bắt buộc nằm NGOÀI</v>
       </c>
-      <c r="G13" t="str">
-        <v>Lỗi thiếu quan hệ kế thừa giữa các Use Case tương ứng</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Lỗi sử dụng sai ký hiệu Actor (người que) thay cho ký hiệu hệ thống</v>
-      </c>
       <c r="I13">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -804,13 +804,13 @@
         <v>Introduction (Giới thiệu) - Overall Description (Mô tả tổng quan) - Specific Requirements (Yêu cầu chi tiết hệ thống)</v>
       </c>
       <c r="F14" t="str">
+        <v>Bug Report (Báo cáo lỗi) - Test Cases (Kịch bản test) - User Manual (Hướng dẫn sử dụng)</v>
+      </c>
+      <c r="G14" t="str">
         <v>Database Schema (Sơ đồ DB) - API List (Danh sách API) - Source Code Structure (Cấu trúc code)</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>User List (Danh sách user) - Project Budget (Ngân sách) - Gantt Chart (Tiến độ dự án)</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Bug Report (Báo cáo lỗi) - Test Cases (Kịch bản test) - User Manual (Hướng dẫn sử dụng)</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -830,19 +830,19 @@
         <v>UAT nghiệm thu dựa trên scope đã thống nhất. Các yêu cầu mới phát sinh ngoài SRS phải đi qua quy trình Change Request để tránh phình to phạm vi dự án một cách mất kiểm soát.</v>
       </c>
       <c r="E15" t="str">
+        <v>Xóa bỏ hoàn toàn tính năng đó khỏi danh sách bàn giao để tránh rắc rối kiểm thử — giảm thiểu rủi ro tiêu cực</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Ghi nhận yêu cầu mới, thực hiện quy trình phân tích thay đổi (Change Request), báo cáo PM/PO để đánh giá ngân sách/tiến độ trước khi quyết định bổ sung — tuân thủ quy trình kiểm soát phạm vi</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Từ chối và báo cáo khách hàng tự chịu trách nhiệm nếu không nghiệm thu được — đối đầu trực tiếp</v>
+      </c>
+      <c r="H15" t="str">
         <v>Đồng ý bổ sung ngay lập tức vào kịch bản UAT và yêu cầu Dev code gấp để kịp nghiệm thu — chiều lòng khách hàng</v>
       </c>
-      <c r="F15" t="str">
-        <v>Từ chối và báo cáo khách hàng tự chịu trách nhiệm nếu không nghiệm thu được — đối đầu trực tiếp</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Ghi nhận yêu cầu mới, thực hiện quy trình phân tích thay đổi (Change Request), báo cáo PM/PO để đánh giá ngân sách/tiến độ trước khi quyết định bổ sung — tuân thủ quy trình kiểm soát phạm vi</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Xóa bỏ hoàn toàn tính năng đó khỏi danh sách bàn giao để tránh rắc rối kiểm thử — giảm thiểu rủi ro tiêu cực</v>
-      </c>
       <c r="I15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -859,19 +859,19 @@
         <v>Đặc tả API của BA đóng vai trò là giao kèo tích hợp (Contract) giữa FE và BE. Cần chỉ rõ URL, method, cấu trúc JSON đầu vào và đầu ra để hai bên phát triển song song.</v>
       </c>
       <c r="E16" t="str">
-        <v>Endpoint URL, HTTP Method (GET/POST/...), Request Payload mẫu, và Response Payload mẫu kèm mô tả ý nghĩa các trường dữ liệu</v>
+        <v>Tên biến và kiểu cấu trúc dữ liệu cụ thể trong code Java/NodeJS của backend</v>
       </c>
       <c r="F16" t="str">
         <v>Cú pháp viết câu lệnh SQL SELECT/INSERT chi tiết để truy vấn vào database</v>
       </c>
       <c r="G16" t="str">
-        <v>Tên biến và kiểu cấu trúc dữ liệu cụ thể trong code Java/NodeJS của backend</v>
+        <v>Màu sắc và khoảng cách padding của button kích hoạt API trên giao diện web</v>
       </c>
       <c r="H16" t="str">
-        <v>Màu sắc và khoảng cách padding của button kích hoạt API trên giao diện web</v>
+        <v>Endpoint URL, HTTP Method (GET/POST/...), Request Payload mẫu, và Response Payload mẫu kèm mô tả ý nghĩa các trường dữ liệu</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>Đường Association (nét liền không mũi tên) kết nối Actor với Use Case để chỉ ra sự tương tác. Đường nét đứt có mũi tên (`&lt;&lt;include&gt;&gt;`/`&lt;&lt;extend&gt;&gt;`) chỉ sự phụ thuộc logic giữa các Use Case.</v>
       </c>
       <c r="E17" t="str">
-        <v>Association kết nối giữa Actor và Use Case; Dependency biểu thị mối quan hệ phụ thuộc giữa các Use Case với nhau</v>
+        <v>Association dùng cho cơ sở dữ liệu; Dependency dùng cho lập trình hướng đối tượng</v>
       </c>
       <c r="F17" t="str">
         <v>Association kết nối các Actor với nhau; Dependency kết nối các Use Case với nhau</v>
       </c>
       <c r="G17" t="str">
+        <v>Association kết nối giữa Actor và Use Case; Dependency biểu thị mối quan hệ phụ thuộc giữa các Use Case với nhau</v>
+      </c>
+      <c r="H17" t="str">
         <v>Association là bắt buộc; Dependency là tùy chọn trong mọi trường hợp thiết kế</v>
       </c>
-      <c r="H17" t="str">
-        <v>Association dùng cho cơ sở dữ liệu; Dependency dùng cho lập trình hướng đối tượng</v>
-      </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>BA hỗ trợ điều phối UAT, giải thích nghiệp vụ, xác định xem lỗi phát sinh là Bug (sai SRS) hay CR (yêu cầu mới ngoài SRS) và lập biên bản nghiệm thu.</v>
       </c>
       <c r="E18" t="str">
+        <v>Làm cầu nối hướng dẫn khách hàng thực hiện theo kịch bản UAT, ghi nhận kết quả nghiệm thu (Pass/Fail) và làm rõ các phản hồi/lỗi nghiệp vụ phát sinh</v>
+      </c>
+      <c r="F18" t="str">
         <v>Lập trình trực tiếp sửa các lỗi phát sinh ngay tại cuộc họp để khách hàng nghiệm thu lại</v>
       </c>
-      <c r="F18" t="str">
-        <v>Làm cầu nối hướng dẫn khách hàng thực hiện theo kịch bản UAT, ghi nhận kết quả nghiệm thu (Pass/Fail) và làm rõ các phản hồi/lỗi nghiệp vụ phát sinh</v>
-      </c>
       <c r="G18" t="str">
+        <v>Thay mặt khách hàng ký biên bản nghiệm thu bàn giao dự án để đẩy nhanh tiến độ thanh toán</v>
+      </c>
+      <c r="H18" t="str">
         <v>Chỉ trích kiểm thử viên của khách hàng nếu họ tìm ra lỗi của đội nhà phát triển</v>
       </c>
-      <c r="H18" t="str">
-        <v>Thay mặt khách hàng ký biên bản nghiệm thu bàn giao dự án để đẩy nhanh tiến độ thanh toán</v>
-      </c>
       <c r="I18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>Vì "In biên lai" là quan hệ `&lt;&lt;extend&gt;&gt;` (tùy chọn), lỗi không in được biên lai không ảnh hưởng đến việc hoàn thành Use Case chính "Rút tiền". Ngược lại, nếu lỗi ở Use Case include "Xác thực mã PIN", giao dịch sẽ thất bại ngay lập tức.</v>
       </c>
       <c r="E19" t="str">
+        <v>Khách hàng vẫn rút được tiền bình thường nhưng hệ thống sẽ bỏ qua bước in biên lai (không thực hiện Use Case mở rộng)</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Hệ thống báo lỗi và không cho khách hàng nhập mã PIN ngay từ đầu vì thiếu điều kiện tiên quyết</v>
+      </c>
+      <c r="G19" t="str">
         <v>Giao dịch rút tiền bị hủy bỏ hoàn toàn vì không thể in được biên lai — hệ thống dừng hoạt động</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Khách hàng vẫn rút được tiền bình thường nhưng hệ thống sẽ bỏ qua bước in biên lai (không thực hiện Use Case mở rộng)</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Hệ thống báo lỗi và không cho khách hàng nhập mã PIN ngay từ đầu vì thiếu điều kiện tiên quyết</v>
       </c>
       <c r="H19" t="str">
         <v>Hệ thống tự động in biên lai ra màn hình điện tử thay vì in giấy vật lý</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -975,19 +975,19 @@
         <v>Khi đặc tả quan hệ `&lt;&lt;extend&gt;&gt;`, tài liệu Use Case Specification của Use Case gốc cần chỉ rõ Extension Point (Vị trí mở rộng trong luồng) và điều kiện cụ thể để kích hoạt Use Case mở rộng.</v>
       </c>
       <c r="E20" t="str">
+        <v>Đặc tả "Đăng nhập sai 3 lần" thành một Exception Flow (luồng ngoại lệ) trong tài liệu Đăng nhập, chỉ định rõ Extension Point và điều kiện kích hoạt luồng mở rộng này</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Tạo một Use Case hoàn toàn độc lập và không kết nối gì với Use Case Đăng nhập chính</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Yêu cầu Dev tự viết logic này trong code, BA không cần đưa vào tài liệu đặc tả</v>
+      </c>
+      <c r="H20" t="str">
         <v>Viết luồng đăng nhập sai thành một bước trong Basic Flow của Use Case Đăng nhập</v>
       </c>
-      <c r="F20" t="str">
-        <v>Đặc tả "Đăng nhập sai 3 lần" thành một Exception Flow (luồng ngoại lệ) trong tài liệu Đăng nhập, chỉ định rõ Extension Point và điều kiện kích hoạt luồng mở rộng này</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Tạo một Use Case hoàn toàn độc lập và không kết nối gì với Use Case Đăng nhập chính</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Yêu cầu Dev tự viết logic này trong code, BA không cần đưa vào tài liệu đặc tả</v>
-      </c>
       <c r="I20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>Nếu phần mềm đúng SRS nhưng sai thực tế, tức là SRS đã bị lỗi thời hoặc BA khơi gợi yêu cầu sai (thiếu Validation động). BA cần xử lý theo quy trình quản lý thay đổi (CR) để cập nhật hệ thống.</v>
       </c>
       <c r="E21" t="str">
+        <v>Lỗi ở giai đoạn kiểm thử (Testing) — QA không phát hiện ra quy trình nghiệp vụ bị thay đổi</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Lỗi ở phía khách hàng — Khách hàng phải tự thay đổi quy trình làm việc của mình theo phần mềm</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Lỗi ở giai đoạn khơi gợi và xác thực yêu cầu (Elicitation &amp; Validation) — BA đã validate tài liệu SRS tĩnh mà không kiểm tra quy trình nghiệp vụ động thực tế. Giải pháp: Lập biên bản ghi nhận thay đổi, phân tích tác động và đề xuất quy trình nâng cấp hệ thống (CR)</v>
+      </c>
+      <c r="H21" t="str">
         <v>Lỗi ở giai đoạn lập trình (Construction) — Dev code sai logic nghiệp vụ thực tế</v>
       </c>
-      <c r="F21" t="str">
-        <v>Lỗi ở giai đoạn khơi gợi và xác thực yêu cầu (Elicitation &amp; Validation) — BA đã validate tài liệu SRS tĩnh mà không kiểm tra quy trình nghiệp vụ động thực tế. Giải pháp: Lập biên bản ghi nhận thay đổi, phân tích tác động và đề xuất quy trình nâng cấp hệ thống (CR)</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Lỗi ở giai đoạn kiểm thử (Testing) — QA không phát hiện ra quy trình nghiệp vụ bị thay đổi</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Lỗi ở phía khách hàng — Khách hàng phải tự thay đổi quy trình làm việc của mình theo phần mềm</v>
-      </c>
       <c r="I21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Sơ đồ Use Case sinh ra để khách hàng hiểu được hệ thống làm gì. Việc lạm dụng chi tiết hóa include/extend biến nó thành sơ đồ thiết kế thuật toán kỹ thuật, mất đi tính giao tiếp nghiệp vụ.</v>
       </c>
       <c r="E22" t="str">
+        <v>Vì làm tăng thời gian chạy của cơ sở dữ liệu khi hệ thống vận hành thực tế</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Vì compiler của Java và C# không hỗ trợ biên dịch các sơ đồ có mối quan hệ này</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Vì trình duyệt không thể render được sơ đồ Use Case nếu có quá nhiều đường nét đứt</v>
+      </c>
+      <c r="H22" t="str">
         <v>Vì làm sơ đồ trở nên quá phức tạp, khó đọc đối với khách hàng (Business stakeholders) và dễ dẫn đến tư duy phân rã chức năng kiểu lập trình (Functional Decomposition) thay vì tập trung vào mục tiêu của tác nhân</v>
       </c>
-      <c r="F22" t="str">
-        <v>Vì trình duyệt không thể render được sơ đồ Use Case nếu có quá nhiều đường nét đứt</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Vì làm tăng thời gian chạy của cơ sở dữ liệu khi hệ thống vận hành thực tế</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Vì compiler của Java và C# không hỗ trợ biên dịch các sơ đồ có mối quan hệ này</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Usability đo lường tính dễ dùng. Để test được, nó phải được lượng hóa thông qua thời gian hoàn thành tác vụ (Task completion time), tỷ lệ lỗi của người dùng (Error rate) và thời gian học sử dụng (Learning curve).</v>
       </c>
       <c r="E23" t="str">
+        <v>Tần suất người dùng mở ứng dụng di động tối thiểu 3 lần một ngày</v>
+      </c>
+      <c r="F23" t="str">
         <v>Mức độ hài lòng của người dùng khi đánh giá giao diện trên thang điểm từ 1 đến 5</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
         <v>Thời gian trung bình một người dùng mới hoàn thành tác vụ cốt lõi không quá 3 phút sau tối đa 15 phút hướng dẫn, và tỷ lệ thực hiện lỗi dưới 5%</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>Số lượng màu sắc phối hợp trên một trang web không được vượt quá 3 tông màu chủ đạo</v>
       </c>
-      <c r="H23" t="str">
-        <v>Tần suất người dùng mở ứng dụng di động tối thiểu 3 lần một ngày</v>
-      </c>
       <c r="I23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>Data Mapping chi tiết (Source Field, Target Field, Type, Rules, Nullability) là bắt buộc để lập trình viên viết code chuyển đổi dữ liệu chính xác, tránh mất mát thông tin hoặc lỗi kiểu dữ liệu ở runtime.</v>
       </c>
       <c r="E24" t="str">
+        <v>Đường truyền mạng internet cáp quang kết nối giữa hai văn phòng công ty</v>
+      </c>
+      <c r="F24" t="str">
         <v>Ánh xạ chi tiết giữa các trường dữ liệu nguồn và đích (Source to Target Field mapping), kiểu dữ liệu, độ dài, quy tắc biến đổi (Transformation rules) và cách xử lý lỗi khi không khớp dữ liệu</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Tên của máy chủ vật lý lưu trữ dữ liệu của cả hai hệ thống</v>
       </c>
       <c r="G24" t="str">
         <v>Danh sách số lượng lập trình viên tham gia viết code tích hợp API của hai bên</v>
       </c>
       <c r="H24" t="str">
-        <v>Đường truyền mạng internet cáp quang kết nối giữa hai văn phòng công ty</v>
+        <v>Tên của máy chủ vật lý lưu trữ dữ liệu của cả hai hệ thống</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Sub-flow giúp chia nhỏ luồng cơ bản dài thành các khối logic tuần tự dễ quản lý. Alternative Flow là nhánh rẽ nghiệp vụ tùy chọn dựa trên quyết định/điều kiện cụ thể.</v>
       </c>
       <c r="E25" t="str">
+        <v>Sub-flow chỉ chạy trên mobile; Alternative Flow chỉ chạy trên môi trường desktop web</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Sub-flow luôn kết thúc bằng lỗi hệ thống; Alternative Flow luôn kết thúc thành công</v>
+      </c>
+      <c r="G25" t="str">
         <v>Sub-flow là một phần của luồng cơ bản được tách ra để dễ đọc (vẫn chạy bắt buộc); Alternative Flow là luồng rẽ nhánh tùy chọn dẫn đến kết quả khác</v>
       </c>
-      <c r="F25" t="str">
+      <c r="H25" t="str">
         <v>Sub-flow do dev viết; Alternative Flow do BA viết tài liệu đặc tả</v>
       </c>
-      <c r="G25" t="str">
-        <v>Sub-flow luôn kết thúc bằng lỗi hệ thống; Alternative Flow luôn kết thúc thành công</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Sub-flow chỉ chạy trên mobile; Alternative Flow chỉ chạy trên môi trường desktop web</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1152,16 +1152,16 @@
         <v>Để dev tự quyết định hoàn toàn vì đây là chi tiết kỹ thuật không liên quan đến BA</v>
       </c>
       <c r="F26" t="str">
+        <v>Viết một file SRS duy nhất và yêu cầu tất cả các dịch vụ sử dụng chung một database tập trung</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Yêu cầu khách hàng cung cấp sơ đồ đi dây mạng của hệ thống máy chủ</v>
+      </c>
+      <c r="H26" t="str">
         <v>Đặc tả rõ ràng luồng nghiệp vụ đi qua các service, kiểu giao tiếp (đồng bộ qua REST/gRPC hay bất đồng bộ qua Message Queue như RabbitMQ/Kafka) và cấu trúc dữ liệu trao đổi giữa các dịch vụ</v>
       </c>
-      <c r="G26" t="str">
-        <v>Viết một file SRS duy nhất và yêu cầu tất cả các dịch vụ sử dụng chung một database tập trung</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Yêu cầu khách hàng cung cấp sơ đồ đi dây mạng của hệ thống máy chủ</v>
-      </c>
       <c r="I26">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
